--- a/data/trans_bre/PCS12_SP_R3-Edad-trans_bre.xlsx
+++ b/data/trans_bre/PCS12_SP_R3-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 3,63</t>
+          <t>-1,65; 4,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 6,27</t>
+          <t>0,29; 6,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,4</t>
+          <t>0,41; 5,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 8,85</t>
+          <t>1,08; 9,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-28,53; 111,69</t>
+          <t>-29,63; 135,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 271,02</t>
+          <t>2,7; 251,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 529,79</t>
+          <t>2,14; 582,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-49,19; 11139,33</t>
+          <t>-28,95; 15262,01</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 7,87</t>
+          <t>2,49; 8,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 3,37</t>
+          <t>-2,73; 3,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 4,85</t>
+          <t>-0,78; 4,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 1,17</t>
+          <t>-8,07; 0,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,71; 241,78</t>
+          <t>44,02; 248,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,21; 64,69</t>
+          <t>-34,67; 68,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,96; 145,9</t>
+          <t>-14,46; 145,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-62,08; 16,0</t>
+          <t>-64,92; 9,52</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 10,38</t>
+          <t>3,65; 10,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 9,34</t>
+          <t>2,3; 9,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 6,1</t>
+          <t>0,01; 6,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 6,59</t>
+          <t>-1,33; 6,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38,66; 187,43</t>
+          <t>40,68; 177,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,04; 125,67</t>
+          <t>21,93; 126,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 105,49</t>
+          <t>-1,02; 111,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 67,69</t>
+          <t>-9,31; 64,59</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,27; 18,13</t>
+          <t>8,37; 17,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 11,16</t>
+          <t>2,28; 11,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 8,6</t>
+          <t>-0,06; 8,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-52,03; 5,23</t>
+          <t>-54,83; 5,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>60,81; 199,17</t>
+          <t>59,73; 189,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,87; 99,04</t>
+          <t>13,35; 99,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 68,89</t>
+          <t>-0,44; 65,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-69,72; 27,9</t>
+          <t>-72,14; 31,44</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 12,1</t>
+          <t>-1,39; 11,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,63; 26,68</t>
+          <t>13,18; 25,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,09; 18,72</t>
+          <t>5,95; 18,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 10,46</t>
+          <t>1,33; 11,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 47,79</t>
+          <t>-4,71; 47,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,13; 132,67</t>
+          <t>49,26; 127,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,27; 90,83</t>
+          <t>21,52; 87,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 36,14</t>
+          <t>3,81; 39,79</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,66; 30,34</t>
+          <t>15,59; 30,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,73; 26,51</t>
+          <t>10,61; 26,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,05; 25,89</t>
+          <t>11,75; 26,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 18,08</t>
+          <t>-21,9; 17,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36,55; 88,78</t>
+          <t>35,61; 88,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,92; 68,9</t>
+          <t>22,45; 68,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,51; 87,5</t>
+          <t>31,11; 88,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-58,45; 59,7</t>
+          <t>-62,44; 56,75</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,76; 22,46</t>
+          <t>5,52; 21,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,93; 20,52</t>
+          <t>6,58; 20,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,41; 21,48</t>
+          <t>5,79; 20,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,89; 26,85</t>
+          <t>16,07; 26,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,41; 36,35</t>
+          <t>7,41; 34,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,98; 31,82</t>
+          <t>8,76; 32,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,75; 36,88</t>
+          <t>8,86; 36,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,75; 50,51</t>
+          <t>26,67; 50,97</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,49; 13,38</t>
+          <t>9,34; 13,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,16; 13,2</t>
+          <t>9,2; 13,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,46; 11,44</t>
+          <t>7,57; 11,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,7; 7,8</t>
+          <t>-16,83; 7,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>57,57; 91,53</t>
+          <t>55,46; 90,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,15; 79,32</t>
+          <t>48,41; 79,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,2; 72,34</t>
+          <t>43,22; 73,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,03; 35,88</t>
+          <t>-39,44; 36,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/PCS12_SP_R3-Edad-trans_bre.xlsx
+++ b/data/trans_bre/PCS12_SP_R3-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,39</t>
+          <t>5,58</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>375,36%</t>
+          <t>377,98%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 4,04</t>
+          <t>-1,45; 3,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 6,04</t>
+          <t>0,14; 6,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,58</t>
+          <t>0,56; 5,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,41</t>
+          <t>1,79; 10,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-29,63; 135,66</t>
+          <t>-27,15; 131,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 251,04</t>
+          <t>1,55; 258,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 582,31</t>
+          <t>4,5; 631,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-28,95; 15262,01</t>
+          <t>17,78; 2205,43</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,99</t>
+          <t>-2,51</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-30,54%</t>
+          <t>-25,6%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 8,05</t>
+          <t>2,35; 7,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 3,38</t>
+          <t>-2,4; 3,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 4,93</t>
+          <t>-0,95; 4,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 0,78</t>
+          <t>-6,98; 1,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,02; 248,04</t>
+          <t>40,12; 235,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,67; 68,98</t>
+          <t>-30,41; 69,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 145,38</t>
+          <t>-16,5; 135,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,92; 9,52</t>
+          <t>-55,98; 23,48</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,69</t>
+          <t>3,78</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>34,18%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,65; 10,2</t>
+          <t>3,58; 9,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 9,16</t>
+          <t>2,48; 9,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,01; 6,41</t>
+          <t>-0,15; 6,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 6,44</t>
+          <t>0,47; 7,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40,68; 177,88</t>
+          <t>40,04; 179,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,93; 126,67</t>
+          <t>22,26; 127,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 111,9</t>
+          <t>-2,37; 105,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 64,59</t>
+          <t>3,39; 83,22</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-17,97</t>
+          <t>4,54</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-43,08%</t>
+          <t>23,02%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,37; 17,38</t>
+          <t>8,36; 17,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 11,11</t>
+          <t>2,79; 11,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 8,47</t>
+          <t>0,03; 8,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-54,83; 5,92</t>
+          <t>0,72; 8,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,73; 189,16</t>
+          <t>61,97; 198,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,35; 99,9</t>
+          <t>17,61; 104,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 65,41</t>
+          <t>-0,15; 68,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-72,14; 31,44</t>
+          <t>3,23; 49,77</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,85</t>
+          <t>7,43</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 11,92</t>
+          <t>-2,11; 11,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,18; 25,83</t>
+          <t>13,26; 26,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,95; 18,67</t>
+          <t>6,26; 18,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 11,34</t>
+          <t>2,8; 12,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 47,87</t>
+          <t>-6,06; 45,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,26; 127,84</t>
+          <t>49,07; 129,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,52; 87,94</t>
+          <t>23,43; 87,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 39,79</t>
+          <t>8,5; 45,2</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>16,51</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-0,81%</t>
+          <t>52,64%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,59; 30,19</t>
+          <t>15,44; 29,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,61; 26,31</t>
+          <t>10,33; 26,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,75; 26,17</t>
+          <t>11,65; 26,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,9; 17,56</t>
+          <t>11,53; 21,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35,61; 88,29</t>
+          <t>36,49; 89,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,45; 68,76</t>
+          <t>22,21; 69,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,11; 88,69</t>
+          <t>32,44; 90,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-62,44; 56,75</t>
+          <t>33,67; 76,66</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21,23</t>
+          <t>21,05</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,81%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,52; 21,18</t>
+          <t>6,25; 20,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,58; 20,86</t>
+          <t>6,58; 21,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,79; 20,72</t>
+          <t>6,99; 21,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,07; 26,83</t>
+          <t>15,64; 26,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,41; 34,27</t>
+          <t>8,63; 33,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,76; 32,75</t>
+          <t>8,83; 33,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,86; 36,19</t>
+          <t>10,44; 37,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26,67; 50,97</t>
+          <t>25,39; 49,73</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>9,17</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>43,35%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,34; 13,56</t>
+          <t>9,48; 13,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,2; 13,57</t>
+          <t>9,09; 13,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,57; 11,55</t>
+          <t>7,3; 11,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 7,78</t>
+          <t>7,25; 11,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>55,46; 90,75</t>
+          <t>56,68; 90,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,41; 79,76</t>
+          <t>48,37; 78,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,22; 73,27</t>
+          <t>41,43; 72,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-39,44; 36,29</t>
+          <t>32,8; 55,14</t>
         </is>
       </c>
     </row>
